--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1,314 +1,184 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="24045" windowHeight="12900"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24045" windowHeight="12900" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <definedNames/>
+  <calcPr calcId="144525" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="40">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>full_name</t>
-  </si>
-  <si>
-    <t>flags</t>
-  </si>
-  <si>
-    <t>unique</t>
-  </si>
-  <si>
-    <t>group</t>
-  </si>
-  <si>
-    <t>comment</t>
-  </si>
-  <si>
-    <t>tags</t>
-  </si>
-  <si>
-    <t>*items</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>alias</t>
-  </si>
-  <si>
-    <t>value</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>全名(包含模块和名字)</t>
-  </si>
-  <si>
-    <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
-  </si>
-  <si>
-    <t>枚举项是否唯一</t>
-  </si>
-  <si>
-    <t>枚举名</t>
-  </si>
-  <si>
-    <t>别名</t>
-  </si>
-  <si>
-    <t>值</t>
-  </si>
-  <si>
-    <t>注释</t>
-  </si>
-  <si>
-    <t>item.EQuality</t>
-  </si>
-  <si>
-    <t>WHITE</t>
-  </si>
-  <si>
-    <t>白</t>
-  </si>
-  <si>
-    <t>最差品质</t>
-  </si>
-  <si>
-    <t>BLUE</t>
-  </si>
-  <si>
-    <t>蓝</t>
-  </si>
-  <si>
-    <t>蓝色的</t>
-  </si>
-  <si>
-    <t>PURPLE</t>
-  </si>
-  <si>
-    <t>紫</t>
-  </si>
-  <si>
-    <t>紫色的</t>
-  </si>
-  <si>
-    <t>RED</t>
-  </si>
-  <si>
-    <t>红</t>
-  </si>
-  <si>
-    <t>最高品质</t>
-  </si>
-  <si>
-    <t>test.AccessFlag</t>
-  </si>
-  <si>
-    <t>WRITE</t>
-  </si>
-  <si>
-    <t>READ</t>
-  </si>
-  <si>
-    <t>TRUNCATE</t>
-  </si>
-  <si>
-    <t>NEW</t>
-  </si>
-  <si>
-    <t>READ_WRITE</t>
-  </si>
-  <si>
-    <t>WRITE|READ</t>
-  </si>
-  <si>
-    <t>位标记使用示例</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="21">
     <font>
-      <sz val="11"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="34">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -506,7 +376,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -627,169 +497,216 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="7">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -843,11 +760,74 @@
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1107,231 +1087,399 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:L12"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L16"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="19" customWidth="1"/>
-    <col min="3" max="3" width="20.8761904761905" customWidth="1"/>
-    <col min="4" max="5" width="14.1238095238095" customWidth="1"/>
-    <col min="6" max="6" width="9.37142857142857" customWidth="1"/>
-    <col min="7" max="7" width="5" customWidth="1"/>
-    <col min="8" max="8" width="13.5047619047619" customWidth="1"/>
-    <col min="9" max="9" width="5.24761904761905" customWidth="1"/>
-    <col min="10" max="10" width="12.1238095238095" customWidth="1"/>
-    <col min="11" max="11" width="15.1238095238095" customWidth="1"/>
+    <col width="19" customWidth="1" style="4" min="2" max="2"/>
+    <col width="20.8761904761905" customWidth="1" style="4" min="3" max="3"/>
+    <col width="14.1238095238095" customWidth="1" style="4" min="4" max="5"/>
+    <col width="9.37142857142857" customWidth="1" style="4" min="6" max="6"/>
+    <col width="5" customWidth="1" style="4" min="7" max="7"/>
+    <col width="13.5047619047619" customWidth="1" style="4" min="8" max="8"/>
+    <col width="5.24761904761905" customWidth="1" style="4" min="9" max="9"/>
+    <col width="12.1238095238095" customWidth="1" style="4" min="10" max="10"/>
+    <col width="15.1238095238095" customWidth="1" style="4" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
-      <c r="A1" s="1" t="s">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>full_name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>flags</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>unique</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>group</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+      <c r="H1" s="2" t="inlineStr">
+        <is>
+          <t>*items</t>
+        </is>
+      </c>
+      <c r="I1" s="5" t="n"/>
+      <c r="J1" s="5" t="n"/>
+      <c r="K1" s="5" t="n"/>
+      <c r="L1" s="6" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n"/>
+      <c r="C2" s="1" t="n"/>
+      <c r="D2" s="1" t="n"/>
+      <c r="E2" s="1" t="n"/>
+      <c r="F2" s="1" t="n"/>
+      <c r="G2" s="1" t="n"/>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>alias</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>comment</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>tags</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="99" customHeight="1" s="4">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="inlineStr">
+        <is>
+          <t>全名(包含模块和名字)</t>
+        </is>
+      </c>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>是否为位标记枚举（即每个枚举项为位标记数据，例如System.IO.FileMode,填数据时可以为READ|WRITE这样)</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>枚举项是否唯一</t>
+        </is>
+      </c>
+      <c r="E3" s="1" t="n"/>
+      <c r="F3" s="1" t="n"/>
+      <c r="G3" s="1" t="n"/>
+      <c r="H3" s="1" t="inlineStr">
+        <is>
+          <t>枚举名</t>
+        </is>
+      </c>
+      <c r="I3" s="1" t="inlineStr">
+        <is>
+          <t>别名</t>
+        </is>
+      </c>
+      <c r="J3" s="1" t="inlineStr">
+        <is>
+          <t>值</t>
+        </is>
+      </c>
+      <c r="K3" s="1" t="inlineStr">
+        <is>
+          <t>注释</t>
+        </is>
+      </c>
+      <c r="L3" s="1" t="n"/>
+    </row>
+    <row r="4">
+      <c r="B4" s="0" t="inlineStr">
+        <is>
+          <t>item.EQuality</t>
+        </is>
+      </c>
+      <c r="C4" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="D4" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H4" s="0" t="inlineStr">
+        <is>
+          <t>WHITE</t>
+        </is>
+      </c>
+      <c r="I4" s="0" t="inlineStr">
+        <is>
+          <t>白</t>
+        </is>
+      </c>
+      <c r="J4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" s="0" t="inlineStr">
+        <is>
+          <t>最差品质</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="H5" s="0" t="inlineStr">
+        <is>
+          <t>BLUE</t>
+        </is>
+      </c>
+      <c r="I5" s="0" t="inlineStr">
+        <is>
+          <t>蓝</t>
+        </is>
+      </c>
+      <c r="J5" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="K5" s="0" t="inlineStr">
+        <is>
+          <t>蓝色的</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="H6" s="0" t="inlineStr">
+        <is>
+          <t>PURPLE</t>
+        </is>
+      </c>
+      <c r="I6" s="0" t="inlineStr">
+        <is>
+          <t>紫</t>
+        </is>
+      </c>
+      <c r="J6" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="K6" s="0" t="inlineStr">
+        <is>
+          <t>紫色的</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="H7" s="0" t="inlineStr">
+        <is>
+          <t>RED</t>
+        </is>
+      </c>
+      <c r="I7" s="0" t="inlineStr">
+        <is>
+          <t>红</t>
+        </is>
+      </c>
+      <c r="J7" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-    </row>
-    <row r="2" spans="1:12">
-      <c r="A2" s="1" t="s">
+      <c r="K7" s="0" t="inlineStr">
+        <is>
+          <t>最高品质</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="0" t="inlineStr">
+        <is>
+          <t>test.AccessFlag</t>
+        </is>
+      </c>
+      <c r="C8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="H8" s="0" t="inlineStr">
+        <is>
+          <t>WRITE</t>
+        </is>
+      </c>
+      <c r="J8" s="0" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="H9" s="0" t="inlineStr">
+        <is>
+          <t>READ</t>
+        </is>
+      </c>
+      <c r="J9" s="0" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="H10" s="0" t="inlineStr">
+        <is>
+          <t>TRUNCATE</t>
+        </is>
+      </c>
+      <c r="J10" s="0" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="H11" s="0" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="J11" s="0" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="H12" s="0" t="inlineStr">
+        <is>
+          <t>READ_WRITE</t>
+        </is>
+      </c>
+      <c r="J12" s="0" t="inlineStr">
+        <is>
+          <t>WRITE|READ</t>
+        </is>
+      </c>
+      <c r="K12" s="0" t="inlineStr">
+        <is>
+          <t>位标记使用示例</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>num.ENumType</t>
+        </is>
+      </c>
+      <c r="C13" t="b">
         <v>0</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" ht="99" customHeight="1" spans="1:12">
-      <c r="A3" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L3" s="1"/>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="B4" t="s">
-        <v>19</v>
-      </c>
-      <c r="C4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" t="b">
+      <c r="D13" t="b">
         <v>1</v>
       </c>
-      <c r="H4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I4" t="s">
-        <v>21</v>
-      </c>
-      <c r="J4">
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>数值底层货币类型(1经验2虔诚币3钻石4体力)</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>EXP</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>经验</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="8:11">
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J5">
+      <c r="K13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>PIETY</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>虔诚币</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
         <v>2</v>
       </c>
-      <c r="K5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="8:11">
-      <c r="H6" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" t="s">
-        <v>27</v>
-      </c>
-      <c r="J6">
+      <c r="K14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>DIAMOND</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>钻石</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
         <v>3</v>
       </c>
-      <c r="K6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="8:11">
-      <c r="H7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I7" t="s">
-        <v>30</v>
-      </c>
-      <c r="J7">
+      <c r="K15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>ENERGY</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>体力</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
         <v>4</v>
       </c>
-      <c r="K7" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" t="b">
-        <v>1</v>
-      </c>
-      <c r="H8" t="s">
-        <v>33</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="8:10">
-      <c r="H9" t="s">
-        <v>34</v>
-      </c>
-      <c r="J9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="8:10">
-      <c r="H10" t="s">
-        <v>35</v>
-      </c>
-      <c r="J10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="8:10">
-      <c r="H11" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="8:11">
-      <c r="H12" t="s">
-        <v>37</v>
-      </c>
-      <c r="J12" t="s">
-        <v>38</v>
-      </c>
-      <c r="K12" t="s">
-        <v>39</v>
-      </c>
+      <c r="K16" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="H1:L1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L16"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
@@ -1396,84 +1396,292 @@
       </c>
     </row>
     <row r="13">
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="0" t="inlineStr">
         <is>
           <t>num.ENumType</t>
         </is>
       </c>
-      <c r="C13" t="b">
+      <c r="C13" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D13" t="b">
+      <c r="D13" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G13" s="0" t="inlineStr">
         <is>
           <t>数值底层货币类型(1经验2虔诚币3钻石4体力)</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H13" s="0" t="inlineStr">
         <is>
           <t>EXP</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I13" s="0" t="inlineStr">
         <is>
           <t>经验</t>
         </is>
       </c>
-      <c r="J13" t="n">
+      <c r="J13" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" s="0" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="H14" t="inlineStr">
+      <c r="H14" s="0" t="inlineStr">
         <is>
           <t>PIETY</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I14" s="0" t="inlineStr">
         <is>
           <t>虔诚币</t>
         </is>
       </c>
-      <c r="J14" t="n">
+      <c r="J14" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" s="0" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="H15" t="inlineStr">
+      <c r="H15" s="0" t="inlineStr">
         <is>
           <t>DIAMOND</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I15" s="0" t="inlineStr">
         <is>
           <t>钻石</t>
         </is>
       </c>
-      <c r="J15" t="n">
+      <c r="J15" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" s="0" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="0" t="inlineStr">
         <is>
           <t>ENERGY</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I16" s="0" t="inlineStr">
         <is>
           <t>体力</t>
         </is>
       </c>
-      <c r="J16" t="n">
+      <c r="J16" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" s="0" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="0" t="inlineStr">
+        <is>
+          <t>item.EItemQuality</t>
+        </is>
+      </c>
+      <c r="C17" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D17" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G17" s="0" t="inlineStr">
+        <is>
+          <t>道具品质(1普通白2高级绿3精英蓝4史诗紫5传说橙6神话红)</t>
+        </is>
+      </c>
+      <c r="H17" s="0" t="inlineStr">
+        <is>
+          <t>COMMON</t>
+        </is>
+      </c>
+      <c r="I17" s="0" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="J17" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" s="0" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="H18" s="0" t="inlineStr">
+        <is>
+          <t>FINE</t>
+        </is>
+      </c>
+      <c r="I18" s="0" t="inlineStr">
+        <is>
+          <t>高级</t>
+        </is>
+      </c>
+      <c r="J18" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" s="0" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="H19" s="0" t="inlineStr">
+        <is>
+          <t>ELITE</t>
+        </is>
+      </c>
+      <c r="I19" s="0" t="inlineStr">
+        <is>
+          <t>精英</t>
+        </is>
+      </c>
+      <c r="J19" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="0" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="H20" s="0" t="inlineStr">
+        <is>
+          <t>EPIC</t>
+        </is>
+      </c>
+      <c r="I20" s="0" t="inlineStr">
+        <is>
+          <t>史诗</t>
+        </is>
+      </c>
+      <c r="J20" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K20" s="0" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="H21" s="0" t="inlineStr">
+        <is>
+          <t>LEGEND</t>
+        </is>
+      </c>
+      <c r="I21" s="0" t="inlineStr">
+        <is>
+          <t>传说</t>
+        </is>
+      </c>
+      <c r="J21" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="K21" s="0" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="H22" s="0" t="inlineStr">
+        <is>
+          <t>MYTH</t>
+        </is>
+      </c>
+      <c r="I22" s="0" t="inlineStr">
+        <is>
+          <t>神话</t>
+        </is>
+      </c>
+      <c r="J22" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="K22" s="0" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>item.EItemType</t>
+        </is>
+      </c>
+      <c r="C23" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>道具类型(1货币2材料3功能材料5自选礼包6随机礼包,跳过4)</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>CURRENCY</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>货币</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>MATERIAL</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>材料</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>2</v>
+      </c>
+      <c r="K24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>FUNC_MATERIAL</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>功能材料</t>
+        </is>
+      </c>
+      <c r="J25" t="n">
+        <v>3</v>
+      </c>
+      <c r="K25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>GIFT_SELECT</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>自选礼包</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>GIFT_RANDOM</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>随机礼包</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>6</v>
+      </c>
+      <c r="K27" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L27"/>
+  <dimension ref="A1:L31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
@@ -1588,100 +1588,192 @@
       <c r="K22" s="0" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr">
         <is>
           <t>item.EItemType</t>
         </is>
       </c>
-      <c r="C23" t="b">
+      <c r="C23" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D23" t="b">
+      <c r="D23" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G23" s="0" t="inlineStr">
         <is>
           <t>道具类型(1货币2材料3功能材料5自选礼包6随机礼包,跳过4)</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H23" s="0" t="inlineStr">
         <is>
           <t>CURRENCY</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I23" s="0" t="inlineStr">
         <is>
           <t>货币</t>
         </is>
       </c>
-      <c r="J23" t="n">
+      <c r="J23" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" s="0" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="H24" t="inlineStr">
+      <c r="H24" s="0" t="inlineStr">
         <is>
           <t>MATERIAL</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I24" s="0" t="inlineStr">
         <is>
           <t>材料</t>
         </is>
       </c>
-      <c r="J24" t="n">
+      <c r="J24" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" s="0" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="H25" t="inlineStr">
+      <c r="H25" s="0" t="inlineStr">
         <is>
           <t>FUNC_MATERIAL</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I25" s="0" t="inlineStr">
         <is>
           <t>功能材料</t>
         </is>
       </c>
-      <c r="J25" t="n">
+      <c r="J25" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" s="0" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="0" t="inlineStr">
         <is>
           <t>GIFT_SELECT</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I26" s="0" t="inlineStr">
         <is>
           <t>自选礼包</t>
         </is>
       </c>
-      <c r="J26" t="n">
+      <c r="J26" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" s="0" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="H27" t="inlineStr">
+      <c r="H27" s="0" t="inlineStr">
         <is>
           <t>GIFT_RANDOM</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I27" s="0" t="inlineStr">
         <is>
           <t>随机礼包</t>
         </is>
       </c>
-      <c r="J27" t="n">
+      <c r="J27" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" s="0" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>avatar.EAvatarType</t>
+        </is>
+      </c>
+      <c r="C28" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>头像类型(1头像2头像框)</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>AVATAR</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>头像</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>FRAME</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>2</v>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>头像框</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>avatar.EUnlockCond</t>
+        </is>
+      </c>
+      <c r="C30" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>解锁条件(1等级2活动发放)</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>LEVEL</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>等级解锁</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>EVENT</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>活动发放</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Configs/GameConfig/Datas/__enums__.xlsx
+++ b/Configs/GameConfig/Datas/__enums__.xlsx
@@ -1092,7 +1092,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L31"/>
+  <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" style="4" min="2" max="2"/>
@@ -1684,96 +1684,336 @@
       <c r="K27" s="0" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="0" t="inlineStr">
         <is>
           <t>avatar.EAvatarType</t>
         </is>
       </c>
-      <c r="C28" t="b">
+      <c r="C28" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D28" t="b">
+      <c r="D28" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="G28" s="0" t="inlineStr">
         <is>
           <t>头像类型(1头像2头像框)</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H28" s="0" t="inlineStr">
         <is>
           <t>AVATAR</t>
         </is>
       </c>
-      <c r="J28" t="n">
+      <c r="J28" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="K28" s="0" t="inlineStr">
         <is>
           <t>头像</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="H29" t="inlineStr">
+      <c r="H29" s="0" t="inlineStr">
         <is>
           <t>FRAME</t>
         </is>
       </c>
-      <c r="J29" t="n">
+      <c r="J29" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="K29" s="0" t="inlineStr">
         <is>
           <t>头像框</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="0" t="inlineStr">
         <is>
           <t>avatar.EUnlockCond</t>
         </is>
       </c>
-      <c r="C30" t="b">
+      <c r="C30" s="0" t="b">
         <v>0</v>
       </c>
-      <c r="D30" t="b">
+      <c r="D30" s="0" t="b">
         <v>1</v>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="0" t="inlineStr">
         <is>
           <t>解锁条件(1等级2活动发放)</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H30" s="0" t="inlineStr">
         <is>
           <t>LEVEL</t>
         </is>
       </c>
-      <c r="J30" t="n">
+      <c r="J30" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="K30" s="0" t="inlineStr">
         <is>
           <t>等级解锁</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="0" t="inlineStr">
         <is>
           <t>EVENT</t>
         </is>
       </c>
-      <c r="J31" t="n">
+      <c r="J31" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="K31" s="0" t="inlineStr">
         <is>
           <t>活动发放</t>
         </is>
       </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="0" t="inlineStr">
+        <is>
+          <t>audio.EAudioType</t>
+        </is>
+      </c>
+      <c r="C32" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" s="0" t="inlineStr">
+        <is>
+          <t>音频粗分类(决定通道池/播放策略)</t>
+        </is>
+      </c>
+      <c r="H32" s="0" t="inlineStr">
+        <is>
+          <t>BGM</t>
+        </is>
+      </c>
+      <c r="I32" s="0" t="inlineStr">
+        <is>
+          <t>背景音乐</t>
+        </is>
+      </c>
+      <c r="J32" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="0" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="H33" s="0" t="inlineStr">
+        <is>
+          <t>GlobalUI</t>
+        </is>
+      </c>
+      <c r="I33" s="0" t="inlineStr">
+        <is>
+          <t>全局UI音效</t>
+        </is>
+      </c>
+      <c r="J33" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" s="0" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="H34" s="0" t="inlineStr">
+        <is>
+          <t>InGame</t>
+        </is>
+      </c>
+      <c r="I34" s="0" t="inlineStr">
+        <is>
+          <t>局内玩法音效</t>
+        </is>
+      </c>
+      <c r="J34" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K34" s="0" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="B35" s="0" t="inlineStr">
+        <is>
+          <t>audio.EAudioGroup</t>
+        </is>
+      </c>
+      <c r="C35" s="0" t="b">
+        <v>0</v>
+      </c>
+      <c r="D35" s="0" t="b">
+        <v>1</v>
+      </c>
+      <c r="G35" s="0" t="inlineStr">
+        <is>
+          <t>音频混音分组(Type的子类型)</t>
+        </is>
+      </c>
+      <c r="H35" s="0" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="I35" s="0" t="inlineStr">
+        <is>
+          <t>全局</t>
+        </is>
+      </c>
+      <c r="J35" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="0" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="H36" s="0" t="inlineStr">
+        <is>
+          <t>BGM</t>
+        </is>
+      </c>
+      <c r="I36" s="0" t="inlineStr">
+        <is>
+          <t>背景音乐</t>
+        </is>
+      </c>
+      <c r="J36" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" s="0" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="H37" s="0" t="inlineStr">
+        <is>
+          <t>UI</t>
+        </is>
+      </c>
+      <c r="I37" s="0" t="inlineStr">
+        <is>
+          <t>界面</t>
+        </is>
+      </c>
+      <c r="J37" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="K37" s="0" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="H38" s="0" t="inlineStr">
+        <is>
+          <t>Battle</t>
+        </is>
+      </c>
+      <c r="I38" s="0" t="inlineStr">
+        <is>
+          <t>战斗</t>
+        </is>
+      </c>
+      <c r="J38" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="K38" s="0" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="H39" s="0" t="inlineStr">
+        <is>
+          <t>Voice</t>
+        </is>
+      </c>
+      <c r="I39" s="0" t="inlineStr">
+        <is>
+          <t>语音</t>
+        </is>
+      </c>
+      <c r="J39" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="K39" s="0" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>audio.EAudioFade</t>
+        </is>
+      </c>
+      <c r="C40" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>淡入淡出模式</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>In</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>仅淡入</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Out</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>仅淡出</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>双向</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>3</v>
+      </c>
+      <c r="K43" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
